--- a/artfynd/A 69304-2021 artfynd.xlsx
+++ b/artfynd/A 69304-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69304-2021 artfynd.xlsx
+++ b/artfynd/A 69304-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102577778</v>
+        <v>102577636</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568612.0233434313</v>
+        <v>568626</v>
       </c>
       <c r="R2" t="n">
-        <v>6675495.216516275</v>
+        <v>6675424</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,56 +783,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102578214</v>
+        <v>102577655</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568747.0187668697</v>
+        <v>568628</v>
       </c>
       <c r="R3" t="n">
-        <v>6675440.079502097</v>
+        <v>6675433</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102577804</v>
+        <v>102577620</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,12 +925,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568649.183467246</v>
+        <v>568650</v>
       </c>
       <c r="R4" t="n">
-        <v>6675584.904691727</v>
+        <v>6675418</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102577620</v>
+        <v>102577657</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,16 +1043,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568649.8279917057</v>
+        <v>568628</v>
       </c>
       <c r="R5" t="n">
-        <v>6675417.870371153</v>
+        <v>6675433</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102578241</v>
+        <v>102577778</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568757.6598464734</v>
+        <v>568613</v>
       </c>
       <c r="R6" t="n">
-        <v>6675430.336050394</v>
+        <v>6675496</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102577657</v>
+        <v>102577794</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1262,11 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568628.1231714995</v>
+        <v>568602</v>
       </c>
       <c r="R7" t="n">
-        <v>6675433.372653262</v>
+        <v>6675509</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,15 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102577794</v>
+        <v>102577804</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568601.7967822765</v>
+        <v>568649</v>
       </c>
       <c r="R8" t="n">
-        <v>6675509.442415101</v>
+        <v>6675585</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,51 +1459,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102577636</v>
+        <v>102578214</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568625.8205145053</v>
+        <v>568747</v>
       </c>
       <c r="R9" t="n">
-        <v>6675423.386024323</v>
+        <v>6675440</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1570,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,57 +1572,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102577655</v>
+        <v>102578241</v>
       </c>
       <c r="B10" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568628.1231714995</v>
+        <v>568758</v>
       </c>
       <c r="R10" t="n">
-        <v>6675433.372653262</v>
+        <v>6675430</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,6 +1678,115 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102578255</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568771</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6675423</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69304-2021 artfynd.xlsx
+++ b/artfynd/A 69304-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577636</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577657</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577778</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577794</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578214</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578241</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,8 +1837,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>